--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484342_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484342_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.9117</v>
+        <v>9.2211</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4071</v>
+        <v>3.6969</v>
       </c>
       <c r="F2" t="n">
-        <v>6.5046</v>
+        <v>5.5242</v>
       </c>
       <c r="G2" t="n">
         <v>4.5472</v>
@@ -610,13 +610,13 @@
         <v>1.9534</v>
       </c>
       <c r="S2" t="n">
-        <v>6.8491</v>
+        <v>3.1585</v>
       </c>
       <c r="T2" t="n">
-        <v>4.8151</v>
+        <v>2.1049</v>
       </c>
       <c r="U2" t="n">
-        <v>2.034</v>
+        <v>1.0535</v>
       </c>
       <c r="V2" t="n">
         <v>2.4921</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5349</v>
+        <v>5.0593</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4404</v>
+        <v>1.8831</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0945</v>
+        <v>3.1762</v>
       </c>
       <c r="G3" t="n">
         <v>1.391</v>
@@ -688,13 +688,13 @@
         <v>1.1721</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6946</v>
+        <v>2.219</v>
       </c>
       <c r="T3" t="n">
-        <v>3.3459</v>
+        <v>1.7886</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3487</v>
+        <v>0.4304</v>
       </c>
       <c r="V3" t="n">
         <v>0.2772</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6935</v>
+        <v>3.5168</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5867</v>
+        <v>0.1005</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2802</v>
+        <v>3.4164</v>
       </c>
       <c r="G4" t="n">
         <v>0.7919</v>
@@ -766,13 +766,13 @@
         <v>2.1488</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7649</v>
+        <v>1.5882</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9520999999999999</v>
+        <v>1.6392</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1872</v>
+        <v>-0.051</v>
       </c>
       <c r="V4" t="n">
         <v>0.9414</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1801</v>
+        <v>1.8985</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.5102</v>
+        <v>-2.8891</v>
       </c>
       <c r="F5" t="n">
-        <v>5.6903</v>
+        <v>4.7877</v>
       </c>
       <c r="G5" t="n">
-        <v>0.717</v>
+        <v>3.8933</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0565</v>
+        <v>1.1543</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6605</v>
+        <v>2.739</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4719</v>
+        <v>2.9235</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3505</v>
+        <v>1.8023</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1214</v>
+        <v>1.1212</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2452</v>
+        <v>0.9699</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2939</v>
+        <v>-0.648</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5391</v>
+        <v>1.6178</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7814</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.9069</v>
+        <v>-4.8836</v>
       </c>
       <c r="R5" t="n">
-        <v>3.1255</v>
+        <v>3.7115</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5803</v>
+        <v>0.5056</v>
       </c>
       <c r="T5" t="n">
-        <v>0.589</v>
+        <v>0.7314000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9913</v>
+        <v>-0.2258</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6642</v>
+        <v>-1.3283</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6642</v>
+        <v>-1.6604</v>
       </c>
       <c r="X5" t="n">
-        <v>1.3283</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4004</v>
+        <v>1.7952</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.2162</v>
+        <v>-3.1869</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6166</v>
+        <v>4.9822</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.482</v>
+        <v>0.717</v>
       </c>
       <c r="H6" t="n">
-        <v>0.65</v>
+        <v>0.0565</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1321</v>
+        <v>0.6605</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.0715</v>
+        <v>0.4719</v>
       </c>
       <c r="K6" t="n">
-        <v>0.33</v>
+        <v>0.3505</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.4015</v>
+        <v>0.1214</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5895</v>
+        <v>0.2452</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3201</v>
+        <v>-0.2939</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2694</v>
+        <v>0.5391</v>
       </c>
       <c r="P6" t="n">
-        <v>0.586</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9534</v>
+        <v>-3.9069</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5395</v>
+        <v>3.1255</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9222</v>
+        <v>1.1954</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4099</v>
+        <v>0.9122</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5124</v>
+        <v>0.2832</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2186</v>
+        <v>0.6642</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2186</v>
+        <v>-0.6642</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.3283</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7040999999999999</v>
+        <v>1.5833</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.7291</v>
+        <v>-1.3873</v>
       </c>
       <c r="F7" t="n">
-        <v>4.0251</v>
+        <v>2.9707</v>
       </c>
       <c r="G7" t="n">
-        <v>3.8933</v>
+        <v>-0.482</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1543</v>
+        <v>0.65</v>
       </c>
       <c r="I7" t="n">
-        <v>2.739</v>
+        <v>-1.1321</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9235</v>
+        <v>-1.0715</v>
       </c>
       <c r="K7" t="n">
-        <v>1.8023</v>
+        <v>0.33</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1212</v>
+        <v>-1.4015</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9699</v>
+        <v>0.5895</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.648</v>
+        <v>0.3201</v>
       </c>
       <c r="O7" t="n">
-        <v>1.6178</v>
+        <v>0.2694</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.8836</v>
+        <v>-1.9534</v>
       </c>
       <c r="R7" t="n">
-        <v>3.7115</v>
+        <v>2.5395</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.097</v>
+        <v>0.2607</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1086</v>
+        <v>0.419</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-0.1583</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3283</v>
+        <v>1.2186</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.6604</v>
+        <v>1.2186</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4481</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1854</v>
+        <v>-1.2149</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7373</v>
+        <v>1.1186</v>
       </c>
       <c r="G8" t="n">
         <v>0.7605</v>
@@ -1078,13 +1078,13 @@
         <v>2.1488</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4859</v>
+        <v>0.866</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3272</v>
+        <v>0.6433</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1586</v>
+        <v>0.2227</v>
       </c>
       <c r="V8" t="n">
         <v>-0.9414</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>G. ALBA ASTOLA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4517</v>
+        <v>-3.5728</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2044</v>
+        <v>-4.7032</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2473</v>
+        <v>1.1305</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5121</v>
+        <v>-3.6869</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.957</v>
+        <v>0.0072</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4449</v>
+        <v>-3.694</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6324</v>
+        <v>-4.2067</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6728</v>
+        <v>0.431</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0405</v>
+        <v>-4.6378</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1203</v>
+        <v>0.5199</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2842</v>
+        <v>-0.4239</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4045</v>
+        <v>0.9437</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8298</v>
+        <v>0.4732</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0456</v>
+        <v>0.4802</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2158</v>
+        <v>-0.007</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.3787</v>
+        <v>-0.5545</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.7145</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. ALBA ASTOLA</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.7261</v>
+        <v>-4.1068</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.7749</v>
+        <v>-2.7505</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0488</v>
+        <v>-1.3562</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.6869</v>
+        <v>-0.5121</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0072</v>
+        <v>-0.957</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.694</v>
+        <v>0.4449</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.2067</v>
+        <v>-0.6324</v>
       </c>
       <c r="K10" t="n">
-        <v>0.431</v>
+        <v>-0.6728</v>
       </c>
       <c r="L10" t="n">
-        <v>-4.6378</v>
+        <v>0.0405</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5199</v>
+        <v>0.1203</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4239</v>
+        <v>-0.2842</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9437</v>
+        <v>0.4045</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6802</v>
+        <v>0.1747</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5915</v>
+        <v>0.4994</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0887</v>
+        <v>-0.3247</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5545</v>
+        <v>-3.3787</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5545</v>
+        <v>-2.7145</v>
       </c>
     </row>
     <row r="11">
@@ -1267,25 +1267,25 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>14.3906</v>
+        <v>15.2984</v>
       </c>
       <c r="E11" t="n">
-        <v>-11.3594</v>
+        <v>-10.4514</v>
       </c>
       <c r="F11" t="n">
-        <v>25.7501</v>
+        <v>25.7503</v>
       </c>
       <c r="G11" t="n">
         <v>7.4199</v>
       </c>
       <c r="H11" t="n">
-        <v>4.0446</v>
+        <v>4.044600000000001</v>
       </c>
       <c r="I11" t="n">
         <v>3.3753</v>
       </c>
       <c r="J11" t="n">
-        <v>2.920800000000001</v>
+        <v>2.9208</v>
       </c>
       <c r="K11" t="n">
         <v>6.2854</v>
@@ -1312,28 +1312,28 @@
         <v>19.5344</v>
       </c>
       <c r="S11" t="n">
-        <v>9.5334</v>
+        <v>10.4413</v>
       </c>
       <c r="T11" t="n">
-        <v>8.310499999999999</v>
+        <v>9.218200000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2229</v>
+        <v>1.223</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6093999999999999</v>
+        <v>-0.6093999999999995</v>
       </c>
       <c r="W11" t="n">
         <v>-1.1031</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4936000000000007</v>
+        <v>0.4935999999999998</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1204</v>
+        <v>-0.1144</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5065</v>
+        <v>-1.4643</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3861</v>
+        <v>1.3499</v>
       </c>
       <c r="G12" t="n">
-        <v>2.0909</v>
+        <v>-1.5081</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3773</v>
+        <v>-0.4694</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7136</v>
+        <v>-1.0387</v>
       </c>
       <c r="J12" t="n">
-        <v>2.1957</v>
+        <v>-0.6695</v>
       </c>
       <c r="K12" t="n">
-        <v>2.1552</v>
+        <v>0.6382</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0405</v>
+        <v>-1.3077</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1048</v>
+        <v>-0.8386</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7779</v>
+        <v>-1.1077</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6731</v>
+        <v>0.269</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1953</v>
+        <v>2.1488</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>2.7348</v>
+        <v>3.1255</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6328</v>
+        <v>-1.864</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0018</v>
+        <v>-0.927</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.6345</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.3832</v>
+        <v>1.1089</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.7739</v>
+        <v>1.1089</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.641</v>
+        <v>-0.1276</v>
       </c>
       <c r="E13" t="n">
         <v>-2.2792</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6381</v>
+        <v>2.1515</v>
       </c>
       <c r="G13" t="n">
         <v>1.0464</v>
@@ -1468,13 +1468,13 @@
         <v>2.5395</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.9413</v>
+        <v>-1.4279</v>
       </c>
       <c r="T13" t="n">
         <v>-0.2859</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.6554</v>
+        <v>-1.142</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3321</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>P. MARTÍNEZ SERRANO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.7613</v>
+        <v>-0.7104</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.8688</v>
+        <v>-0.6522</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1075</v>
+        <v>-0.0582</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.5081</v>
+        <v>-0.6267</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4694</v>
+        <v>-0.9366</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.0387</v>
+        <v>0.3099</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.6695</v>
+        <v>-0.5518</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6382</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.3077</v>
+        <v>0.0405</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8386</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1077</v>
+        <v>-0.3443</v>
       </c>
       <c r="O14" t="n">
-        <v>0.269</v>
+        <v>0.2694</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="R14" t="n">
-        <v>3.1255</v>
+        <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.5109</v>
+        <v>-0.2325</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3315</v>
+        <v>0.095</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1794</v>
+        <v>-0.3275</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1089</v>
+        <v>-1.2186</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1089</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ SERRANO</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.9671</v>
+        <v>-0.7271</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.8544</v>
+        <v>-1.5177</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1127</v>
+        <v>0.7906</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6267</v>
+        <v>2.0909</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9366</v>
+        <v>1.3773</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3099</v>
+        <v>0.7136</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5518</v>
+        <v>2.1957</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5921999999999999</v>
+        <v>2.1552</v>
       </c>
       <c r="L15" t="n">
         <v>0.0405</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.07489999999999999</v>
+        <v>-0.1048</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3443</v>
+        <v>-0.7779</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2694</v>
+        <v>0.6731</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3674</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1953</v>
+        <v>-2.9301</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5627</v>
+        <v>2.7348</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4892</v>
+        <v>-1.2395</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1073</v>
+        <v>-0.0094</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3819</v>
+        <v>-1.2301</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2186</v>
+        <v>-1.3832</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2186</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>M. FONTANALS MARTIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9902</v>
+        <v>-1.0664</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.8442</v>
+        <v>-3.1047</v>
       </c>
       <c r="F16" t="n">
-        <v>0.854</v>
+        <v>2.0383</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.3693</v>
+        <v>-0.5639</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.4771</v>
+        <v>-0.4285</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1078</v>
+        <v>-0.1354</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3311</v>
+        <v>-0.284</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3044</v>
+        <v>-0.284</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0266</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0382</v>
+        <v>-0.2799</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1727</v>
+        <v>-0.1445</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1344</v>
+        <v>-0.1354</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1953</v>
+        <v>-0.586</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>-3.1255</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7581</v>
+        <v>2.5395</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7538</v>
+        <v>-0.3033</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4404</v>
+        <v>0.3048</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.1942</v>
+        <v>-0.6082</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3283</v>
+        <v>0.3869</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.3283</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>R. PALOMARES MUÑOZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0844</v>
+        <v>-1.1648</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.2058</v>
+        <v>-2.8877</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1214</v>
+        <v>1.7229</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5639</v>
+        <v>-2.8668</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4285</v>
+        <v>-0.7091</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1354</v>
+        <v>-2.1577</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.284</v>
+        <v>-3.1863</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.284</v>
+        <v>-0.4899</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-2.6964</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2799</v>
+        <v>0.3195</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1445</v>
+        <v>-0.2192</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1354</v>
+        <v>0.5387</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.1255</v>
+        <v>-0.1953</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5395</v>
+        <v>1.3674</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3214</v>
+        <v>0.1431</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2037</v>
+        <v>0.494</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5251</v>
+        <v>-0.3509</v>
       </c>
       <c r="V17" t="n">
         <v>0.3869</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.397</v>
+        <v>-1.6422</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.6854</v>
+        <v>-4.4408</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2885</v>
+        <v>2.7985</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.8668</v>
+        <v>-0.3158</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7091</v>
+        <v>-0.9895</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.1577</v>
+        <v>0.6737</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.1863</v>
+        <v>-0.5705</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4899</v>
+        <v>-0.5705</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.6964</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3195</v>
+        <v>0.2547</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2192</v>
+        <v>-0.419</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5387</v>
+        <v>0.6737</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1721</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1953</v>
+        <v>-4.1022</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0891</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6962</v>
+        <v>-0.0453</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7853</v>
+        <v>0.5942</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3869</v>
+        <v>0.6642</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X18" t="n">
         <v>0.3869</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. BERTOMEU BALDÉ</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4919</v>
+        <v>-1.6643</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8712</v>
+        <v>-2.6531</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3793</v>
+        <v>0.9888</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9196</v>
+        <v>-1.3693</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7391</v>
+        <v>-1.4771</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6587</v>
+        <v>0.1078</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9295</v>
+        <v>-0.3311</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3249</v>
+        <v>-0.3044</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2544</v>
+        <v>-0.0266</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-1.0382</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4142</v>
+        <v>-1.1727</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4043</v>
+        <v>0.1344</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.1255</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9534</v>
+        <v>1.7581</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0209</v>
+        <v>-1.4279</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3247</v>
+        <v>-0.3686</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3456</v>
+        <v>-1.0594</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2186</v>
+        <v>1.3283</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2186</v>
+        <v>1.3283</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>J. BERTOMEU BALDÉ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2203</v>
+        <v>-1.6863</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.0474</v>
+        <v>-2.1746</v>
       </c>
       <c r="F20" t="n">
-        <v>2.8271</v>
+        <v>0.4882</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3158</v>
+        <v>0.9196</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9895</v>
+        <v>-0.7391</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6737</v>
+        <v>1.6587</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5705</v>
+        <v>0.9295</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5705</v>
+        <v>-0.3249</v>
       </c>
       <c r="L20" t="n">
+        <v>1.2544</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-0.009900000000000001</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-0.4142</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.4043</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-3.1255</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.2153</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.0214</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.2367</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W20" t="n">
         <v>0</v>
       </c>
-      <c r="M20" t="n">
-        <v>0.2547</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-0.419</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.6737</v>
-      </c>
-      <c r="P20" t="n">
-        <v>-2.5395</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>-4.1022</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.5627</v>
-      </c>
-      <c r="S20" t="n">
-        <v>-0.0292</v>
-      </c>
-      <c r="T20" t="n">
-        <v>-0.652</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.6228</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0.6642</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0.2772</v>
-      </c>
       <c r="X20" t="n">
-        <v>0.3869</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.7171</v>
+        <v>-3.4649</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.5873</v>
+        <v>-4.5761</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8702</v>
+        <v>1.1112</v>
       </c>
       <c r="G21" t="n">
         <v>-4.2262</v>
@@ -2092,13 +2092,13 @@
         <v>2.3441</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.7448</v>
+        <v>-1.4926</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.5131</v>
+        <v>-0.5019</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.2317</v>
+        <v>-0.9907</v>
       </c>
       <c r="V21" t="n">
         <v>0.8865</v>
@@ -2125,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-14.3907</v>
+        <v>-12.3684</v>
       </c>
       <c r="E22" t="n">
-        <v>-25.7502</v>
+        <v>-25.7504</v>
       </c>
       <c r="F22" t="n">
-        <v>11.3595</v>
+        <v>13.3817</v>
       </c>
       <c r="G22" t="n">
-        <v>-7.4199</v>
+        <v>-7.419900000000001</v>
       </c>
       <c r="H22" t="n">
         <v>-4.0445</v>
@@ -2170,19 +2170,19 @@
         <v>21.4877</v>
       </c>
       <c r="S22" t="n">
-        <v>-9.5334</v>
+        <v>-7.510999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.223</v>
+        <v>-1.2229</v>
       </c>
       <c r="U22" t="n">
-        <v>-8.310300000000002</v>
+        <v>-6.2883</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6092000000000002</v>
+        <v>0.6092000000000003</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.4937000000000005</v>
+        <v>-0.4937</v>
       </c>
       <c r="X22" t="n">
         <v>1.1029</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484342_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484342_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>1.3283</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484342_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>1.3283</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484342_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484342_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,11 +881,16 @@
       <c r="X5" t="n">
         <v>0.3321</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484342_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7952</v>
+        <v>1.8279</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.1869</v>
+        <v>1.8279</v>
       </c>
       <c r="F6" t="n">
-        <v>4.9822</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.717</v>
+        <v>1.8279</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0565</v>
+        <v>0.614</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6605</v>
+        <v>1.214</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4719</v>
+        <v>1.8279</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3505</v>
+        <v>0.614</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1214</v>
+        <v>1.214</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2452</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2939</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5391</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1255</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1954</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9122</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2832</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.3283</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484342_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5833</v>
+        <v>1.7952</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3873</v>
+        <v>-3.1869</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9707</v>
+        <v>4.9822</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.482</v>
+        <v>0.717</v>
       </c>
       <c r="H7" t="n">
-        <v>0.65</v>
+        <v>0.0565</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1321</v>
+        <v>0.6605</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.0715</v>
+        <v>0.4719</v>
       </c>
       <c r="K7" t="n">
-        <v>0.33</v>
+        <v>0.3505</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4015</v>
+        <v>0.1214</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5895</v>
+        <v>0.2452</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3201</v>
+        <v>-0.2939</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2694</v>
+        <v>0.5391</v>
       </c>
       <c r="P7" t="n">
-        <v>0.586</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9534</v>
+        <v>-3.9069</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5395</v>
+        <v>3.1255</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2607</v>
+        <v>1.1954</v>
       </c>
       <c r="T7" t="n">
-        <v>0.419</v>
+        <v>0.9122</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1583</v>
+        <v>0.2832</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2186</v>
+        <v>0.6642</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2186</v>
+        <v>-0.6642</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.3283</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484342_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.09619999999999999</v>
+        <v>1.5833</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2149</v>
+        <v>-1.3873</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1186</v>
+        <v>2.9707</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7605</v>
+        <v>-0.482</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3303</v>
+        <v>0.65</v>
       </c>
       <c r="I8" t="n">
-        <v>2.0908</v>
+        <v>-1.1321</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7947</v>
+        <v>-1.0715</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4874</v>
+        <v>0.33</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2821</v>
+        <v>-1.4015</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0342</v>
+        <v>0.5895</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8429</v>
+        <v>0.3201</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8087</v>
+        <v>0.2694</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1488</v>
+        <v>2.5395</v>
       </c>
       <c r="S8" t="n">
-        <v>0.866</v>
+        <v>0.2607</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6433</v>
+        <v>0.419</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2227</v>
+        <v>-0.1583</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9414</v>
+        <v>1.2186</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484342_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. ALBA ASTOLA</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5728</v>
+        <v>-1.9242</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.7032</v>
+        <v>-3.0428</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1305</v>
+        <v>1.1186</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.6869</v>
+        <v>-1.0674</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0072</v>
+        <v>-1.9442</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.694</v>
+        <v>0.8768</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.2067</v>
+        <v>-1.0332</v>
       </c>
       <c r="K9" t="n">
-        <v>0.431</v>
+        <v>-1.1013</v>
       </c>
       <c r="L9" t="n">
-        <v>-4.6378</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5199</v>
+        <v>-0.0342</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4239</v>
+        <v>-0.8429</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9437</v>
+        <v>0.8087</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1953</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1721</v>
+        <v>2.1488</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4732</v>
+        <v>0.866</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4802</v>
+        <v>0.6433</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.007</v>
+        <v>0.2227</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5545</v>
+        <v>-0.9414</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5545</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484342_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>G. ALBA ASTOLA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1068</v>
+        <v>-3.5728</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7505</v>
+        <v>-4.7032</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3562</v>
+        <v>1.1305</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5121</v>
+        <v>-3.6869</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.957</v>
+        <v>0.0072</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4449</v>
+        <v>-3.694</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6324</v>
+        <v>-4.2067</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6728</v>
+        <v>0.431</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0405</v>
+        <v>-4.6378</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1203</v>
+        <v>0.5199</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2842</v>
+        <v>-0.4239</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4045</v>
+        <v>0.9437</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1747</v>
+        <v>0.4732</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4994</v>
+        <v>0.4802</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3247</v>
+        <v>-0.007</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.3787</v>
+        <v>-0.5545</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.7145</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484342_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,526 +1317,552 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>15.2984</v>
+        <v>-4.1068</v>
       </c>
       <c r="E11" t="n">
-        <v>-10.4514</v>
+        <v>-2.7505</v>
       </c>
       <c r="F11" t="n">
-        <v>25.7503</v>
+        <v>-1.3562</v>
       </c>
       <c r="G11" t="n">
-        <v>7.4199</v>
+        <v>-0.5121</v>
       </c>
       <c r="H11" t="n">
-        <v>4.044600000000001</v>
+        <v>-0.957</v>
       </c>
       <c r="I11" t="n">
-        <v>3.3753</v>
+        <v>0.4449</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9208</v>
+        <v>-0.6324</v>
       </c>
       <c r="K11" t="n">
-        <v>6.2854</v>
+        <v>-0.6728</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.3645</v>
+        <v>0.0405</v>
       </c>
       <c r="M11" t="n">
-        <v>4.499400000000001</v>
+        <v>0.1203</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.2408</v>
+        <v>-0.2842</v>
       </c>
       <c r="O11" t="n">
-        <v>6.7399</v>
+        <v>0.4045</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.9536</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q11" t="n">
-        <v>-21.4876</v>
+        <v>-1.9534</v>
       </c>
       <c r="R11" t="n">
-        <v>19.5344</v>
+        <v>1.5627</v>
       </c>
       <c r="S11" t="n">
-        <v>10.4413</v>
+        <v>0.1747</v>
       </c>
       <c r="T11" t="n">
-        <v>9.218200000000001</v>
+        <v>0.4994</v>
       </c>
       <c r="U11" t="n">
-        <v>1.223</v>
+        <v>-0.3247</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6093999999999995</v>
+        <v>-3.3787</v>
       </c>
       <c r="W11" t="n">
-        <v>-1.1031</v>
+        <v>-0.6642</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4935999999999998</v>
+        <v>-2.7145</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484342_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>CB NAVÀS VISCOLA</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1144</v>
+        <v>15.2983</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4643</v>
+        <v>-10.4514</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3499</v>
+        <v>25.7503</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.5081</v>
+        <v>7.4199</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4694</v>
+        <v>4.044700000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.0387</v>
+        <v>3.3753</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6695</v>
+        <v>2.9208</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6382</v>
+        <v>6.2855</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3077</v>
+        <v>-3.3645</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8386</v>
+        <v>4.499400000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1077</v>
+        <v>-2.2408</v>
       </c>
       <c r="O12" t="n">
-        <v>0.269</v>
+        <v>6.7399</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1488</v>
+        <v>-1.9536</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9767</v>
+        <v>-21.4876</v>
       </c>
       <c r="R12" t="n">
-        <v>3.1255</v>
+        <v>19.5344</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.864</v>
+        <v>10.4413</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.927</v>
+        <v>9.218200000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9370000000000001</v>
+        <v>1.223000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>1.1089</v>
+        <v>-0.6093999999999995</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1089</v>
+        <v>-1.1031</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
-      </c>
+        <v>0.4935999999999998</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>E. MARTIN GASCON</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1276</v>
+        <v>-0.1144</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2792</v>
+        <v>-1.4643</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1515</v>
+        <v>1.3499</v>
       </c>
       <c r="G13" t="n">
-        <v>1.0464</v>
+        <v>-1.5081</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4518</v>
+        <v>-0.4694</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4054</v>
+        <v>-1.0387</v>
       </c>
       <c r="J13" t="n">
-        <v>1.6206</v>
+        <v>-0.6695</v>
       </c>
       <c r="K13" t="n">
-        <v>2.2947</v>
+        <v>0.6382</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6741</v>
+        <v>-1.3077</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5743</v>
+        <v>-0.8386</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8429</v>
+        <v>-1.1077</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2687</v>
+        <v>0.269</v>
       </c>
       <c r="P13" t="n">
-        <v>0.586</v>
+        <v>2.1488</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>2.5395</v>
+        <v>3.1255</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4279</v>
+        <v>-1.864</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2859</v>
+        <v>-0.927</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.142</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3321</v>
+        <v>1.1089</v>
       </c>
       <c r="W13" t="n">
-        <v>-1.6604</v>
+        <v>1.1089</v>
       </c>
       <c r="X13" t="n">
-        <v>1.3283</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484342_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ SERRANO</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.7104</v>
+        <v>-0.1276</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.6522</v>
+        <v>-2.2792</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0582</v>
+        <v>2.1515</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6267</v>
+        <v>1.0464</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.9366</v>
+        <v>1.4518</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3099</v>
+        <v>-0.4054</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5518</v>
+        <v>1.6206</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.5921999999999999</v>
+        <v>2.2947</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0405</v>
+        <v>-0.6741</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.07489999999999999</v>
+        <v>-0.5743</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3443</v>
+        <v>-0.8429</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2694</v>
+        <v>0.2687</v>
       </c>
       <c r="P14" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1953</v>
+        <v>-1.9534</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5627</v>
+        <v>2.5395</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2325</v>
+        <v>-1.4279</v>
       </c>
       <c r="T14" t="n">
-        <v>0.095</v>
+        <v>-0.2859</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3275</v>
+        <v>-1.142</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2186</v>
+        <v>-0.3321</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>-1.6604</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2186</v>
+        <v>1.3283</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484342_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>P. MARTINEZ SERRANO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.7271</v>
+        <v>-0.7104</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.5177</v>
+        <v>-0.6522</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7906</v>
+        <v>-0.0582</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0909</v>
+        <v>-0.6267</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3773</v>
+        <v>-0.9366</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7136</v>
+        <v>0.3099</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1957</v>
+        <v>-0.5518</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1552</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="L15" t="n">
         <v>0.0405</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1048</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7779</v>
+        <v>-0.3443</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6731</v>
+        <v>0.2694</v>
       </c>
       <c r="P15" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="Q15" t="n">
         <v>-0.1953</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-2.9301</v>
-      </c>
       <c r="R15" t="n">
-        <v>2.7348</v>
+        <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2395</v>
+        <v>-0.2325</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0094</v>
+        <v>0.095</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.2301</v>
+        <v>-0.3275</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.3832</v>
+        <v>-1.2186</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.7739</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6093</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484342_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.0664</v>
+        <v>-0.7271</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.1047</v>
+        <v>-1.5177</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0383</v>
+        <v>0.7906</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5639</v>
+        <v>2.0909</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4285</v>
+        <v>1.3773</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1354</v>
+        <v>0.7136</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.284</v>
+        <v>2.1957</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.284</v>
+        <v>2.1552</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.0405</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2799</v>
+        <v>-0.1048</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1445</v>
+        <v>-0.7779</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1354</v>
+        <v>0.6731</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.586</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.1255</v>
+        <v>-2.9301</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5395</v>
+        <v>2.7348</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3033</v>
+        <v>-1.2395</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3048</v>
+        <v>-0.0094</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6082</v>
+        <v>-1.2301</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3869</v>
+        <v>-1.3832</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3869</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484342_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>M. FONTANALS MARTIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1648</v>
+        <v>-1.0664</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.8877</v>
+        <v>-3.1047</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7229</v>
+        <v>2.0383</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.8668</v>
+        <v>-0.5639</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7091</v>
+        <v>-0.4285</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.1577</v>
+        <v>-0.1354</v>
       </c>
       <c r="J17" t="n">
-        <v>-3.1863</v>
+        <v>-0.284</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4899</v>
+        <v>-0.284</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.6964</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3195</v>
+        <v>-0.2799</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2192</v>
+        <v>-0.1445</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5387</v>
+        <v>-0.1354</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1721</v>
+        <v>-0.586</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1953</v>
+        <v>-3.1255</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3674</v>
+        <v>2.5395</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1431</v>
+        <v>-0.3033</v>
       </c>
       <c r="T17" t="n">
-        <v>0.494</v>
+        <v>0.3048</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3509</v>
+        <v>-0.6082</v>
       </c>
       <c r="V17" t="n">
         <v>0.3869</v>
@@ -1796,397 +1872,506 @@
       </c>
       <c r="X17" t="n">
         <v>0.3869</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484342_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>R. PALOMARES MUNOZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6422</v>
+        <v>-1.1648</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.4408</v>
+        <v>-2.8877</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7985</v>
+        <v>1.7229</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3158</v>
+        <v>-2.8668</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9895</v>
+        <v>-0.7091</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6737</v>
+        <v>-2.1577</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5705</v>
+        <v>-3.1863</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5705</v>
+        <v>-0.4899</v>
       </c>
       <c r="L18" t="n">
+        <v>-2.6964</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.2192</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.5387</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.1431</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.3509</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="W18" t="n">
         <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.2547</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-0.419</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.6737</v>
-      </c>
-      <c r="P18" t="n">
-        <v>-2.5395</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>-4.1022</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.5627</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.5489000000000001</v>
-      </c>
-      <c r="T18" t="n">
-        <v>-0.0453</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.5942</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0.6642</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.2772</v>
       </c>
       <c r="X18" t="n">
         <v>0.3869</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484342_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6643</v>
+        <v>-1.6422</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.6531</v>
+        <v>-4.4408</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9888</v>
+        <v>2.7985</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3693</v>
+        <v>-0.3158</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4771</v>
+        <v>-0.9895</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1078</v>
+        <v>0.6737</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3311</v>
+        <v>-0.5705</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3044</v>
+        <v>-0.5705</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0266</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0382</v>
+        <v>0.2547</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1727</v>
+        <v>-0.419</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1344</v>
+        <v>0.6737</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1953</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>-4.1022</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4279</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3686</v>
+        <v>-0.0453</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0594</v>
+        <v>0.5942</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3283</v>
+        <v>0.6642</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X19" t="n">
-        <v>1.3283</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484342_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. BERTOMEU BALDÉ</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6863</v>
+        <v>-1.6643</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1746</v>
+        <v>-2.6531</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4882</v>
+        <v>0.9888</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9196</v>
+        <v>-1.3693</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7391</v>
+        <v>-1.4771</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6587</v>
+        <v>0.1078</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9295</v>
+        <v>-0.3311</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3249</v>
+        <v>-0.3044</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2544</v>
+        <v>-0.0266</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-1.0382</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4142</v>
+        <v>-1.1727</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4043</v>
+        <v>0.1344</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.1255</v>
+        <v>-1.9534</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9534</v>
+        <v>1.7581</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2153</v>
+        <v>-1.4279</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0214</v>
+        <v>-0.3686</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2367</v>
+        <v>-1.0594</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2186</v>
+        <v>1.3283</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>1.3283</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484342_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>J. BERTOMEU BALDE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4649</v>
+        <v>-1.6863</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.5761</v>
+        <v>-2.1746</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1112</v>
+        <v>0.4882</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.2262</v>
+        <v>0.9196</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1243</v>
+        <v>-0.7391</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.1018</v>
+        <v>1.6587</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.6519</v>
+        <v>0.9295</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2814</v>
+        <v>-0.3249</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.3705</v>
+        <v>1.2544</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5743</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8429</v>
+        <v>-0.4142</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2687</v>
+        <v>0.4043</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3674</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>-3.1255</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3441</v>
+        <v>1.9534</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4926</v>
+        <v>-0.2153</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5019</v>
+        <v>0.0214</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9907</v>
+        <v>-0.2367</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8865</v>
+        <v>-1.2186</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3321</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484342_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
+        <v>-3.4649</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-4.5761</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.1112</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-4.2262</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-1.1243</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-3.1018</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-3.6519</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-0.2814</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-3.3705</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.5743</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.8429</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.2687</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.3441</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-1.4926</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.5019</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.9907</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.8865</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484342_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
         <v>-12.3684</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E23" t="n">
         <v>-25.7504</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F23" t="n">
         <v>13.3817</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G23" t="n">
         <v>-7.419900000000001</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H23" t="n">
         <v>-4.0445</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I23" t="n">
         <v>-3.3753</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>-4.4993</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>2.2408</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L23" t="n">
         <v>-6.7399</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M23" t="n">
         <v>-2.9207</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N23" t="n">
         <v>-6.2853</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O23" t="n">
         <v>3.3646</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P23" t="n">
         <v>1.9535</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q23" t="n">
         <v>-19.5341</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R23" t="n">
         <v>21.4877</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S23" t="n">
         <v>-7.510999999999999</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T23" t="n">
         <v>-1.2229</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U23" t="n">
         <v>-6.2883</v>
       </c>
-      <c r="V22" t="n">
+      <c r="V23" t="n">
         <v>0.6092000000000003</v>
       </c>
-      <c r="W22" t="n">
+      <c r="W23" t="n">
         <v>-0.4937</v>
       </c>
-      <c r="X22" t="n">
+      <c r="X23" t="n">
         <v>1.1029</v>
       </c>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
